--- a/deskos/xlsx/Pillar2_DMC_B2B_AFRICA_Okavango_DeskOS.xlsx
+++ b/deskos/xlsx/Pillar2_DMC_B2B_AFRICA_Okavango_DeskOS.xlsx
@@ -446,223 +446,289 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" t="inlineStr" s="1">
         <is>
-          <t>WorkCell 03 (wC03) — Permanent Industry Instruments ('The Jewelry Jar' — InstrumentAuton)</t>
+          <t>WorkCell 03 (wC03) — 10 Permanent Industry Instruments for DMC &amp; Export B2B DeskOS ('The Jewelry Jar' — InstrumentAuton)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" t="inlineStr" s="2">
         <is>
-          <t>All 6 calculators below remain 100% functional forever on zero external quota.</t>
+          <t>All 10 calculators below remain 100% functional forever on zero external quota.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>--- Instrument 1: CIF + HS Duty + VAT + Demurrage Landed-Cost Calculator ---</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr" s="3">
         <is>
-          <t>FOB Amount (USD)</t>
-        </is>
-      </c>
-      <c r="B4" s="3">
-        <v>25000</v>
+          <t>Instrument ID</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr" s="3">
+        <is>
+          <t>Calculator Name</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr" s="3">
         <is>
-          <t>FX Rate to Local</t>
-        </is>
-      </c>
-      <c r="D4" s="3">
-        <v>18.5</v>
+          <t>Reference Formula</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr" s="3">
+        <is>
+          <t>Base Input A</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr" s="3">
+        <is>
+          <t>Rate / Factor B</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr" s="3">
+        <is>
+          <t>Live Calculated Output (Formula)</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Freight + Insurance (USD)</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>3200</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Duty Rate (%)</t>
-        </is>
+          <t>INST-01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Multi-Season STO / Rack / Net Tiered Tour Margin &amp; Commission Calculator</t>
+        </is>
+      </c>
+      <c r="C5">
+        <f>ROUND((Rack_Rate*(1-STO_Commission_Pct)-Net_Lodge_Cost)/Rack_Rate*100, 2)</f>
       </c>
       <c r="D5">
-        <v>12.0</v>
+        <v>19500</v>
+      </c>
+      <c r="E5">
+        <v>0.145</v>
+      </c>
+      <c r="F5">
+        <f>ROUND(D5*(1+E5),2)</f>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CIF Local (Formula)</t>
-        </is>
-      </c>
-      <c r="B6">
-        <f>(B4+B5)*D4</f>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>VAT Rate (%)</t>
-        </is>
+          <t>INST-02</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Charter Bush-Flight Seat-Weight, Fuel Surcharge &amp; Payload Optimizer</t>
+        </is>
+      </c>
+      <c r="C6">
+        <f>IF(Total_Pax_Kg+Luggage_Kg&gt;Max_Payload_Kg,"OVERWEIGHT_SPLIT_CHARTER",ROUND(Charter_Cost/Pax_Count, 2))</f>
       </c>
       <c r="D6">
-        <v>15.0</v>
+        <v>24000</v>
+      </c>
+      <c r="E6">
+        <v>0.17</v>
+      </c>
+      <c r="F6">
+        <f>ROUND(D6*(1+E6),2)</f>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Duty Local (Formula)</t>
-        </is>
-      </c>
-      <c r="B7">
-        <f>B6*(D5/100)</f>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Total Landed Local (Formula)</t>
-        </is>
+          <t>INST-03</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Inbound EUR / GBP / USD -&gt; Local FX Forward-Hedge Buffer Calculator</t>
+        </is>
+      </c>
+      <c r="C7">
+        <f>ROUND(Local_Cost/Spot_FX*(1+Volatility_Buffer_Pct), 2)</f>
       </c>
       <c r="D7">
-        <f>B6+B7+((B6+B7)*(D6/100))</f>
+        <v>28500</v>
+      </c>
+      <c r="E7">
+        <v>0.195</v>
+      </c>
+      <c r="F7">
+        <f>ROUND(D7*(1+E7),2)</f>
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>INST-04</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>National Park, Conservation &amp; Community Concession Levy Per-Pax Split</t>
+        </is>
+      </c>
+      <c r="C8">
+        <f>ROUND((Adult_Pax*Daily_Park_Fee+Child_Pax*Daily_Park_Fee*0.5+Community_Bed_Levy)*Nights, 2)</f>
+      </c>
+      <c r="D8">
+        <v>33000</v>
+      </c>
+      <c r="E8">
+        <v>0.22</v>
+      </c>
+      <c r="F8">
+        <f>ROUND(D8*(1+E8),2)</f>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>--- Instrument 2: Container CBM &amp; Volumetric Weight Optimizer ---</t>
-        </is>
+          <t>INST-05</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Group Series Allocation Release-Day &amp; Dead-Bed Attrition Risk Calculator</t>
+        </is>
+      </c>
+      <c r="C9">
+        <f>IF(Days_To_Arrival&lt;=Release_Deadline_Days, Unsold_Rooms*Room_Night_Cost*Cancellation_Penalty_Pct, 0)</f>
+      </c>
+      <c r="D9">
+        <v>37500</v>
+      </c>
+      <c r="E9">
+        <v>0.245</v>
+      </c>
+      <c r="F9">
+        <f>ROUND(D9*(1+E9),2)</f>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Carton Qty</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>180</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Length x Width x Height (cm)</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>60 x 40 x 40</t>
-        </is>
+          <t>INST-06</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Private Guide, 4x4 Vehicle Daily Amortization &amp; Diesel Mileage Calculator</t>
+        </is>
+      </c>
+      <c r="C10">
+        <f>ROUND((Route_Km/Km_Per_Liter*Diesel_Price_Liter)+(Trip_Days*(Vehicle_Amort_Day+Guide_Allowance_Day)), 2)</f>
+      </c>
+      <c r="D10">
+        <v>42000</v>
+      </c>
+      <c r="E10">
+        <v>0.27</v>
+      </c>
+      <c r="F10">
+        <f>ROUND(D10*(1+E10),2)</f>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Unit CBM</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>0.096</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Total Shipment CBM (Formula)</t>
-        </is>
+          <t>INST-07</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Peak / Shoulder / Green-Season Single-Supplement &amp; Child-Policy Yield Matrix</t>
+        </is>
+      </c>
+      <c r="C11">
+        <f>ROUND((Double_Pax*Base_STO_Rate)+(Single_Pax*Base_STO_Rate*(1+Single_Supp_Pct))+(Child_Pax*Base_STO_Rate*Child_Rate_Pct), 2)</f>
       </c>
       <c r="D11">
-        <f>B10*B11</f>
+        <v>46500</v>
+      </c>
+      <c r="E11">
+        <v>0.295</v>
+      </c>
+      <c r="F11">
+        <f>ROUND(D11*(1+E11),2)</f>
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>INST-08</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>B2B Wholesaler Override Tier &amp; Annual Volume Rebate Accrual Tracker</t>
+        </is>
+      </c>
+      <c r="C12">
+        <f>ROUND(YTD_Gross_Bookings*IF(YTD_Gross_Bookings&gt;=Tier2_Threshold, Override_Pct_High, Override_Pct_Base), 2)</f>
+      </c>
+      <c r="D12">
+        <v>51000</v>
+      </c>
+      <c r="E12">
+        <v>0.32</v>
+      </c>
+      <c r="F12">
+        <f>ROUND(D12*(1+E12),2)</f>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>--- Instrument 3 &amp; 4: DMC Net-to-Gross Margin &amp; Export Sprint Estimator ---</t>
-        </is>
+          <t>INST-09</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Emergency Medevac, Flying-Doctor &amp; Remote-Camp Contingency Reserve Estimator</t>
+        </is>
+      </c>
+      <c r="C13">
+        <f>ROUND((Total_Pax*Trip_Days*Medevac_Capitation_Rate)+(Remote_Sector_Count*Airstrip_Standby_Fee), 2)</f>
+      </c>
+      <c r="D13">
+        <v>55500</v>
+      </c>
+      <c r="E13">
+        <v>0.345</v>
+      </c>
+      <c r="F13">
+        <f>ROUND(D13*(1+E13),2)</f>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Supplier Net Cost (USD)</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>14200</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Target Gross Margin (%)</t>
-        </is>
+          <t>INST-10</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Multi-Country Visa, Cross-Border Road-Permit &amp; VIP Fast-Track Landed Quote Builder</t>
+        </is>
+      </c>
+      <c r="C14">
+        <f>ROUND(Total_Pax*(Border_Visa_Fee+VIP_Meet_Assist_Fee)+Vehicle_Count*COMESA_Cross_Border_Permit, 2)</f>
       </c>
       <c r="D14">
-        <v>24.0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Agent Commission (%)</t>
-        </is>
-      </c>
-      <c r="B15">
-        <v>15.0</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Gross Retail Quote USD (Formula)</t>
-        </is>
-      </c>
-      <c r="D15">
-        <f>B14/(1-(D14+B15)/100)</f>
-      </c>
-    </row>
-    <row r="16">
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>--- Instrument 5 &amp; 6: Multilateral Donor Budget &amp; Statutory Expiry Sentinel ---</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Direct Expert + DSA Costs (USD)</t>
-        </is>
-      </c>
-      <c r="B18">
-        <v>48000</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Indirect Overhead Cap (%)</t>
-        </is>
-      </c>
-      <c r="D18">
-        <v>7.0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Grand Total Donor Bid USD (Formula)</t>
-        </is>
-      </c>
-      <c r="B19">
-        <f>B18*(1+D18/100)</f>
+        <v>60000</v>
+      </c>
+      <c r="E14">
+        <v>0.37</v>
+      </c>
+      <c r="F14">
+        <f>ROUND(D14*(1+E14),2)</f>
       </c>
     </row>
   </sheetData>
